--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ZENTRO BASKET MADRID.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>80.86660000000001</v>
+        <v>66.29340000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>50.5675</v>
+        <v>49.09459999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>30.2993</v>
+        <v>17.1988</v>
       </c>
       <c r="G2" t="n">
-        <v>20.6156</v>
+        <v>46.3708</v>
       </c>
       <c r="H2" t="n">
-        <v>23.423</v>
+        <v>23.4687</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.8076</v>
+        <v>22.9019</v>
       </c>
       <c r="J2" t="n">
-        <v>35.1343</v>
+        <v>67.22279999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>29.6435</v>
+        <v>41.5893</v>
       </c>
       <c r="L2" t="n">
-        <v>5.4908</v>
+        <v>25.6328</v>
       </c>
       <c r="M2" t="n">
-        <v>-14.5188</v>
+        <v>-20.8518</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.2211</v>
+        <v>-18.121</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.297700000000001</v>
+        <v>-2.7308</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5820000000000005</v>
+        <v>-13.7762</v>
       </c>
       <c r="Q2" t="n">
-        <v>-54.32899999999999</v>
+        <v>-62.4786</v>
       </c>
       <c r="R2" t="n">
-        <v>54.911</v>
+        <v>48.7019</v>
       </c>
       <c r="S2" t="n">
-        <v>54.2514</v>
+        <v>9.0831</v>
       </c>
       <c r="T2" t="n">
-        <v>37.9554</v>
+        <v>5.8029</v>
       </c>
       <c r="U2" t="n">
-        <v>16.2963</v>
+        <v>3.2802</v>
       </c>
       <c r="V2" t="n">
-        <v>5.4179</v>
+        <v>24.6161</v>
       </c>
       <c r="W2" t="n">
-        <v>31.8071</v>
+        <v>38.5475</v>
       </c>
       <c r="X2" t="n">
-        <v>-26.3891</v>
+        <v>-13.9314</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9977</v>
+        <v>49.0812</v>
       </c>
       <c r="E3" t="n">
-        <v>41.8589</v>
+        <v>25.3894</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1389</v>
+        <v>23.6914</v>
       </c>
       <c r="G3" t="n">
-        <v>46.3708</v>
+        <v>20.6156</v>
       </c>
       <c r="H3" t="n">
-        <v>23.4687</v>
+        <v>23.423</v>
       </c>
       <c r="I3" t="n">
-        <v>22.9019</v>
+        <v>-2.8076</v>
       </c>
       <c r="J3" t="n">
-        <v>67.22279999999999</v>
+        <v>35.1343</v>
       </c>
       <c r="K3" t="n">
-        <v>41.5893</v>
+        <v>29.6435</v>
       </c>
       <c r="L3" t="n">
-        <v>25.6328</v>
+        <v>5.4908</v>
       </c>
       <c r="M3" t="n">
-        <v>-20.8518</v>
+        <v>-14.5188</v>
       </c>
       <c r="N3" t="n">
-        <v>-18.121</v>
+        <v>-6.2211</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.7308</v>
+        <v>-8.297700000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-13.7762</v>
+        <v>0.5820000000000005</v>
       </c>
       <c r="Q3" t="n">
-        <v>-62.4786</v>
+        <v>-54.32899999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>48.7019</v>
+        <v>54.911</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2129</v>
+        <v>22.4658</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4328</v>
+        <v>12.7772</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7799</v>
+        <v>9.688499999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>24.6161</v>
+        <v>5.4179</v>
       </c>
       <c r="W3" t="n">
-        <v>38.5475</v>
+        <v>31.8071</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.9314</v>
+        <v>-26.3891</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>44.0228</v>
+        <v>41.0712</v>
       </c>
       <c r="E4" t="n">
-        <v>30.4335</v>
+        <v>30.08</v>
       </c>
       <c r="F4" t="n">
-        <v>13.5894</v>
+        <v>10.991</v>
       </c>
       <c r="G4" t="n">
         <v>54.2566</v>
@@ -766,13 +766,13 @@
         <v>48.7019</v>
       </c>
       <c r="S4" t="n">
-        <v>9.8682</v>
+        <v>6.9163</v>
       </c>
       <c r="T4" t="n">
-        <v>2.71</v>
+        <v>2.3568</v>
       </c>
       <c r="U4" t="n">
-        <v>7.1576</v>
+        <v>4.5592</v>
       </c>
       <c r="V4" t="n">
         <v>6.092700000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. VIÑO LOPEZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>22.4078</v>
+        <v>26.3913</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9798</v>
+        <v>23.344</v>
       </c>
       <c r="F5" t="n">
-        <v>3.427900000000001</v>
+        <v>3.047399999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4733</v>
+        <v>5.8346</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5582</v>
+        <v>13.573</v>
       </c>
       <c r="I5" t="n">
-        <v>11.9153</v>
+        <v>-7.7385</v>
       </c>
       <c r="J5" t="n">
-        <v>29.3508</v>
+        <v>36.6988</v>
       </c>
       <c r="K5" t="n">
-        <v>15.2664</v>
+        <v>32.1356</v>
       </c>
       <c r="L5" t="n">
-        <v>14.0844</v>
+        <v>4.563099999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.8774</v>
+        <v>-30.8644</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.7084</v>
+        <v>-18.5624</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1691</v>
+        <v>-12.3019</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>18.433</v>
       </c>
       <c r="Q5" t="n">
-        <v>-21.7317</v>
+        <v>-32.2095</v>
       </c>
       <c r="R5" t="n">
-        <v>21.7316</v>
+        <v>50.6425</v>
       </c>
       <c r="S5" t="n">
-        <v>3.179</v>
+        <v>-0.2598</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7607</v>
+        <v>-0.4888</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4183</v>
+        <v>0.2289</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2446999999999999</v>
+        <v>2.383700000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>9.5998</v>
+        <v>19.3432</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.8446</v>
+        <v>-16.9594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>N. VIÑO LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5314</v>
+        <v>23.6531</v>
       </c>
       <c r="E6" t="n">
-        <v>16.0921</v>
+        <v>19.3642</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5608</v>
+        <v>4.2888</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8346</v>
+        <v>19.4733</v>
       </c>
       <c r="H6" t="n">
-        <v>13.573</v>
+        <v>7.5582</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.7385</v>
+        <v>11.9153</v>
       </c>
       <c r="J6" t="n">
-        <v>36.6988</v>
+        <v>29.3508</v>
       </c>
       <c r="K6" t="n">
-        <v>32.1356</v>
+        <v>15.2664</v>
       </c>
       <c r="L6" t="n">
-        <v>4.563099999999999</v>
+        <v>14.0844</v>
       </c>
       <c r="M6" t="n">
-        <v>-30.8644</v>
+        <v>-9.8774</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.5624</v>
+        <v>-7.7084</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.3019</v>
+        <v>-2.1691</v>
       </c>
       <c r="P6" t="n">
-        <v>18.433</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.2095</v>
+        <v>-21.7317</v>
       </c>
       <c r="R6" t="n">
-        <v>50.6425</v>
+        <v>21.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-12.1196</v>
+        <v>4.4243</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.7407</v>
+        <v>2.145</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.3794</v>
+        <v>2.2793</v>
       </c>
       <c r="V6" t="n">
-        <v>2.383700000000001</v>
+        <v>-0.2446999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>19.3432</v>
+        <v>9.5998</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.9594</v>
+        <v>-9.8446</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>8.404199999999999</v>
+        <v>5.469799999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3134</v>
+        <v>2.5417</v>
       </c>
       <c r="F7" t="n">
-        <v>7.0909</v>
+        <v>2.928100000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6665999999999996</v>
+        <v>0.7246</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0898000000000001</v>
+        <v>-2.3944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7563</v>
+        <v>3.118899999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2735</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0556</v>
+        <v>2.4966</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2179</v>
+        <v>6.3835</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6072</v>
+        <v>-8.1555</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1456</v>
+        <v>-4.8906</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4614999999999999</v>
+        <v>-3.2645</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3285</v>
+        <v>8.343500000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.9853</v>
+        <v>-8.925599999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.313499999999999</v>
+        <v>17.2691</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4467</v>
+        <v>-1.7355</v>
       </c>
       <c r="T7" t="n">
-        <v>4.9819</v>
+        <v>0.4691</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4649</v>
+        <v>-2.2049</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0373</v>
+        <v>-1.8627</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04330000000000034</v>
+        <v>2.1179</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0806</v>
+        <v>-3.9806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GARCIA DELGADO</t>
+          <t>S. COULIBALY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4793</v>
+        <v>5.1963</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6239999999999997</v>
+        <v>-1.6079</v>
       </c>
       <c r="F8" t="n">
-        <v>4.103199999999999</v>
+        <v>6.8043</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4727999999999999</v>
+        <v>0.6665999999999996</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1684</v>
+        <v>-0.0898000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6955</v>
+        <v>0.7563</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7736999999999998</v>
+        <v>3.2735</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0021</v>
+        <v>2.0556</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2283</v>
+        <v>1.2179</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3009999999999999</v>
+        <v>-2.6072</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1662</v>
+        <v>-2.1456</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4673</v>
+        <v>-0.4614999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>5.238799999999999</v>
+        <v>2.3285</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9404</v>
+        <v>-6.9853</v>
       </c>
       <c r="R8" t="n">
-        <v>7.1791</v>
+        <v>9.313499999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6308999999999999</v>
+        <v>3.2389</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8199000000000001</v>
+        <v>2.0605</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1888</v>
+        <v>1.1783</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6015</v>
+        <v>-1.0373</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3627</v>
+        <v>0.04330000000000034</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9642</v>
+        <v>-1.0806</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>D. GARCIA DELGADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.510199999999999</v>
+        <v>4.3279</v>
       </c>
       <c r="E9" t="n">
-        <v>8.898600000000002</v>
+        <v>-0.1023999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.388800000000001</v>
+        <v>4.4303</v>
       </c>
       <c r="G9" t="n">
-        <v>-13.5139</v>
+        <v>0.4727999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.8265</v>
+        <v>2.1684</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.687399999999999</v>
+        <v>-1.6955</v>
       </c>
       <c r="J9" t="n">
-        <v>9.678899999999999</v>
+        <v>0.7736999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>12.3005</v>
+        <v>2.0021</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6215</v>
+        <v>-1.2283</v>
       </c>
       <c r="M9" t="n">
-        <v>-23.193</v>
+        <v>-0.3009999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-19.1273</v>
+        <v>0.1662</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.065700000000001</v>
+        <v>-0.4673</v>
       </c>
       <c r="P9" t="n">
-        <v>13.3883</v>
+        <v>5.238799999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.6573</v>
+        <v>-1.9404</v>
       </c>
       <c r="R9" t="n">
-        <v>31.0453</v>
+        <v>7.1791</v>
       </c>
       <c r="S9" t="n">
-        <v>6.4029</v>
+        <v>0.2176000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>4.829</v>
+        <v>-0.2984</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5737</v>
+        <v>0.5158999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.7672</v>
+        <v>-1.6015</v>
       </c>
       <c r="W9" t="n">
-        <v>12.0478</v>
+        <v>1.3627</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.8149</v>
+        <v>-2.9642</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9684</v>
+        <v>2.3355</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2648</v>
+        <v>3.7652</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2963</v>
+        <v>-1.4297</v>
       </c>
       <c r="G10" t="n">
         <v>7.6027</v>
@@ -1234,13 +1234,13 @@
         <v>6.9851</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.4686</v>
+        <v>-2.1015</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8854</v>
+        <v>-1.3849</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5829</v>
+        <v>-0.7166000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-5.300000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7214999999999989</v>
+        <v>1.387499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>6.254800000000001</v>
+        <v>5.978100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.5331</v>
+        <v>-4.590599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6625</v>
@@ -1312,13 +1312,13 @@
         <v>25.2242</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6679</v>
+        <v>2.3336</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2518</v>
+        <v>1.975</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5839</v>
+        <v>0.3587999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7763</v>
@@ -1345,13 +1345,13 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3350999999999995</v>
+        <v>0.7537000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4459000000000001</v>
+        <v>0.8673000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1106000000000001</v>
+        <v>-0.1135000000000003</v>
       </c>
       <c r="G12" t="n">
         <v>2.3043</v>
@@ -1390,13 +1390,13 @@
         <v>5.4328</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3084999999999999</v>
+        <v>0.7271</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04239999999999987</v>
+        <v>0.4637999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2660999999999999</v>
+        <v>0.2631</v>
       </c>
       <c r="V12" t="n">
         <v>-4.8</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8130999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5475</v>
+        <v>6.8412</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7346</v>
+        <v>-6.1633</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7246</v>
+        <v>-13.5139</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3944</v>
+        <v>-6.8265</v>
       </c>
       <c r="I13" t="n">
-        <v>3.118899999999999</v>
+        <v>-6.687399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>8.880000000000001</v>
+        <v>9.678899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4966</v>
+        <v>12.3005</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3835</v>
+        <v>-2.6215</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.1555</v>
+        <v>-23.193</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.8906</v>
+        <v>-19.1273</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2645</v>
+        <v>-4.065700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8.343500000000001</v>
+        <v>13.3883</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.925599999999999</v>
+        <v>-17.6573</v>
       </c>
       <c r="R13" t="n">
-        <v>17.2691</v>
+        <v>31.0453</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.0183</v>
+        <v>4.5709</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6201</v>
+        <v>2.7716</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3983</v>
+        <v>1.7994</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8627</v>
+        <v>-3.7672</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1179</v>
+        <v>12.0478</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.9806</v>
+        <v>-15.8149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7381</v>
+        <v>-1.331100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>5.130399999999999</v>
+        <v>-4.0639</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.8681</v>
+        <v>2.732699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.2226</v>
+        <v>-8.1553</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.4821</v>
+        <v>-6.2112</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7403999999999997</v>
+        <v>-1.944100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>6.3287</v>
+        <v>5.4528</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8583</v>
+        <v>2.7972</v>
       </c>
       <c r="L14" t="n">
-        <v>4.4707</v>
+        <v>2.655600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.5514</v>
+        <v>-13.6082</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.3403</v>
+        <v>-9.0085</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.211</v>
+        <v>-4.5994</v>
       </c>
       <c r="P14" t="n">
-        <v>7.7614</v>
+        <v>12.8062</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.5227</v>
+        <v>-16.8809</v>
       </c>
       <c r="R14" t="n">
-        <v>23.2842</v>
+        <v>29.6869</v>
       </c>
       <c r="S14" t="n">
-        <v>6.1351</v>
+        <v>1.7178</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8781</v>
+        <v>0.4940000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2571</v>
+        <v>1.2242</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.411900000000001</v>
+        <v>-7.7002</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4462</v>
+        <v>6.870200000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.8581</v>
+        <v>-14.5701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ANIKE</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.7285</v>
+        <v>-2.4639</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3814</v>
+        <v>-2.305</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3471</v>
+        <v>-0.159</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5141</v>
+        <v>-3.3891</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.251</v>
+        <v>-0.8181</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7368</v>
+        <v>-2.5709</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0817</v>
+        <v>-1.4668</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8898</v>
+        <v>0.5478</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9715</v>
+        <v>-2.0148</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5958</v>
+        <v>-1.9222</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.3612</v>
+        <v>-1.3661</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2346</v>
+        <v>-0.5561</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0487</v>
+        <v>-0.0451</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.775</v>
+        <v>0.132</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2736</v>
+        <v>-0.1773</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9418</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. ANIKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.8376</v>
+        <v>-3.0583</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.4061</v>
+        <v>0.019</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4315000000000001</v>
+        <v>-3.0773</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.3891</v>
+        <v>-2.5141</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8181</v>
+        <v>-3.251</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5709</v>
+        <v>0.7368</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4668</v>
+        <v>1.0817</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5478</v>
+        <v>-0.8898</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.0148</v>
+        <v>1.9715</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9222</v>
+        <v>-3.5958</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3661</v>
+        <v>-2.3612</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5561</v>
+        <v>-1.2346</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4189</v>
+        <v>-0.3785</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9691</v>
+        <v>-0.3746</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4498</v>
+        <v>-0.0039</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.283000000000001</v>
+        <v>-4.2379</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.3918</v>
+        <v>4.1134</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1088</v>
+        <v>-8.351099999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.1553</v>
+        <v>-11.2226</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.2112</v>
+        <v>-10.4821</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.944100000000001</v>
+        <v>-0.7403999999999997</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4528</v>
+        <v>6.3287</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7972</v>
+        <v>1.8583</v>
       </c>
       <c r="L17" t="n">
-        <v>2.655600000000001</v>
+        <v>4.4707</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.6082</v>
+        <v>-17.5514</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.0085</v>
+        <v>-12.3403</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.5994</v>
+        <v>-5.211</v>
       </c>
       <c r="P17" t="n">
-        <v>12.8062</v>
+        <v>7.7614</v>
       </c>
       <c r="Q17" t="n">
-        <v>-16.8809</v>
+        <v>-15.5227</v>
       </c>
       <c r="R17" t="n">
-        <v>29.6869</v>
+        <v>23.2842</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.2338</v>
+        <v>3.6352</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.834</v>
+        <v>2.8611</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4000000000000001</v>
+        <v>0.7742</v>
       </c>
       <c r="V17" t="n">
-        <v>-7.7002</v>
+        <v>-4.411900000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>6.870200000000001</v>
+        <v>10.4462</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.5701</v>
+        <v>-14.8581</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-20.7486</v>
+        <v>-9.577199999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-26.359</v>
+        <v>-19.4654</v>
       </c>
       <c r="F18" t="n">
-        <v>5.610100000000001</v>
+        <v>9.8881</v>
       </c>
       <c r="G18" t="n">
         <v>-19.5225</v>
@@ -1858,13 +1858,13 @@
         <v>41.3289</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.5154</v>
+        <v>0.6565000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-6.7737</v>
+        <v>0.1197999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.7416</v>
+        <v>0.5367</v>
       </c>
       <c r="V18" t="n">
         <v>37.8116</v>
@@ -1891,13 +1891,13 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.8289</v>
+        <v>-14.4827</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.7327</v>
+        <v>-12.1824</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.0964</v>
+        <v>-2.300199999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-17.1182</v>
@@ -1936,13 +1936,13 @@
         <v>38.6127</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.7614</v>
+        <v>3.5846</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.6624</v>
+        <v>1.8877</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.099</v>
+        <v>1.6969</v>
       </c>
       <c r="V19" t="n">
         <v>-10.0685</v>
@@ -1969,22 +1969,22 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>170.2672</v>
+        <v>191.4877</v>
       </c>
       <c r="E20" t="n">
-        <v>123.7972</v>
+        <v>131.6711</v>
       </c>
       <c r="F20" t="n">
-        <v>46.4704</v>
+        <v>59.81620000000001</v>
       </c>
       <c r="G20" t="n">
         <v>80.22370000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>71.60160000000002</v>
+        <v>71.6016</v>
       </c>
       <c r="I20" t="n">
-        <v>8.620800000000003</v>
+        <v>8.620799999999996</v>
       </c>
       <c r="J20" t="n">
         <v>319.276</v>
@@ -1993,7 +1993,7 @@
         <v>231.6517</v>
       </c>
       <c r="L20" t="n">
-        <v>87.62360000000001</v>
+        <v>87.6236</v>
       </c>
       <c r="M20" t="n">
         <v>-239.0534</v>
@@ -2014,13 +2014,13 @@
         <v>463.7373</v>
       </c>
       <c r="S20" t="n">
-        <v>37.8312</v>
+        <v>59.0513</v>
       </c>
       <c r="T20" t="n">
-        <v>25.89620000000001</v>
+        <v>33.7698</v>
       </c>
       <c r="U20" t="n">
-        <v>11.9344</v>
+        <v>25.2809</v>
       </c>
       <c r="V20" t="n">
         <v>32.8099</v>
